--- a/firefighter_forms/022_fire_service_recovery_leave_of_absence_form--firefighter_forms.xlsx
+++ b/firefighter_forms/022_fire_service_recovery_leave_of_absence_form--firefighter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'less_than_1_week',_'label':_'less_than_1_week'}</t>
+          <t>less_than_1_week</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'less_than_1_week', 'label': 'Less than 1 week'}</t>
+          <t>Less than 1 week</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'1_2_weeks',_'label':_'1-2_weeks'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': '1_2_weeks', 'label': '1-2 weeks'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'3_4_weeks',_'label':_'3-4_weeks'}</t>
+          <t>3-4_weeks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': '3_4_weeks', 'label': '3-4 weeks'}</t>
+          <t>3-4 weeks</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'more_than_4_weeks',_'label':_'more_than_4_weeks'}</t>
+          <t>more_than_4_weeks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'more_than_4_weeks', 'label': 'More than 4 weeks'}</t>
+          <t>More than 4 weeks</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'administration',_'label':_'administration'}</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'administration', 'label': 'Administration'}</t>
+          <t>Administration</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'fire',_'label':_'fire'}</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'fire', 'label': 'Fire'}</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'operations',_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'operations', 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'bereavement',_'label':_'bereavement'}</t>
+          <t>bereavement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'bereavement', 'label': 'Bereavement'}</t>
+          <t>Bereavement</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'court',_'label':_'court'}</t>
+          <t>court</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'court', 'label': 'Court'}</t>
+          <t>Court</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'doctor',_'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'doctor', 'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'family',_'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'family', 'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'jury',_'label':_'jury'}</t>
+          <t>jury</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'jury', 'label': 'Jury'}</t>
+          <t>Jury</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
